--- a/changes/hk416-handguards.xlsx
+++ b/changes/hk416-handguards.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yifan/Documents/deadline-balancing/changes/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WhyTh\Documents\GitHub\deadline-balancing\changes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E10F1878-7112-A74D-8875-645448E1E826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46E07321-263F-4215-89EE-52103C2A38CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="m4-barrels" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="53">
   <si>
     <t>new</t>
   </si>
@@ -144,6 +144,54 @@
   </si>
   <si>
     <t>kf_416_long_qd_hkey_handguard</t>
+  </si>
+  <si>
+    <t>vallais_mfh_kf_mlok_10.5inch_handguard</t>
+  </si>
+  <si>
+    <t>northeast_industries_416_mlok_9inch_handguard</t>
+  </si>
+  <si>
+    <t>northeast_industries_416_mlok_13.5inch_handguard</t>
+  </si>
+  <si>
+    <t>Northeast Industries 416 MLOK 9"</t>
+  </si>
+  <si>
+    <t>Northeast Industries 416 MLOK 13.5"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vallais_mfh_kf_mlok_14.5inch_handguard </t>
+  </si>
+  <si>
+    <t>Vallais MFH KF MLOK 10.5"</t>
+  </si>
+  <si>
+    <t>Vallais MFH KF MLOK 14.5"</t>
+  </si>
+  <si>
+    <t>vallais_2_hole_misc_rail</t>
+  </si>
+  <si>
+    <t>vallais_2_hole_grip_compat_rail</t>
+  </si>
+  <si>
+    <t>vallais_3_hole_misc_rail</t>
+  </si>
+  <si>
+    <t>vallais_3_hole_grip_compat_rail</t>
+  </si>
+  <si>
+    <t>nariakira_vallais_kf_rail_indexer</t>
+  </si>
+  <si>
+    <t>Vallais 2 Hole Accessory</t>
+  </si>
+  <si>
+    <t>Vallais 3 Hole Accessory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nariakira Vallais KF Rail </t>
   </si>
 </sst>
 </file>
@@ -984,19 +1032,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:R29"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.33203125" customWidth="1"/>
+    <col min="1" max="1" width="39.140625" customWidth="1"/>
     <col min="2" max="2" width="49" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="C1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1040,7 +1088,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -1077,366 +1125,576 @@
         <v>0.26119999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>17</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" t="s">
         <v>25</v>
       </c>
-      <c r="C4">
+      <c r="C5">
         <v>9</v>
       </c>
-      <c r="D4">
+      <c r="D5">
         <v>0.31</v>
       </c>
-      <c r="E4">
+      <c r="E5">
         <v>-10</v>
       </c>
-      <c r="F4">
+      <c r="F5">
         <v>-14</v>
       </c>
-      <c r="M4">
+      <c r="M5">
         <v>0</v>
       </c>
-      <c r="N4">
-        <f t="shared" ref="N4:N13" si="0">C4-D4*20-E4*0.8-F4*0.6-H4*5+I4*10+J4/300</f>
+      <c r="N5">
+        <f t="shared" ref="N5:N30" si="0">C5-D5*20-E5*0.8-F5*0.6-H5*5+I5*10+J5/300</f>
         <v>19.200000000000003</v>
       </c>
-      <c r="P4">
+      <c r="P5">
         <v>160</v>
       </c>
-      <c r="Q4">
+      <c r="Q5">
         <v>0.03</v>
       </c>
-      <c r="R4">
-        <f t="shared" ref="R4:R13" si="1">P4*0.0013+0.07+Q4</f>
+      <c r="R5">
+        <f t="shared" ref="R5:R18" si="1">P5*0.0013+0.07+Q5</f>
         <v>0.30800000000000005</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>18</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" t="s">
         <v>26</v>
       </c>
-      <c r="C5">
+      <c r="C6">
         <v>7</v>
       </c>
-      <c r="D5">
+      <c r="D6">
         <v>0.34</v>
       </c>
-      <c r="E5">
+      <c r="E6">
         <v>-12</v>
       </c>
-      <c r="F5">
+      <c r="F6">
         <v>-16</v>
       </c>
-      <c r="M5">
+      <c r="M6">
         <v>500</v>
       </c>
-      <c r="N5">
+      <c r="N6">
         <f t="shared" si="0"/>
         <v>19.399999999999999</v>
       </c>
-      <c r="P5">
+      <c r="P6">
         <v>187</v>
       </c>
-      <c r="Q5">
+      <c r="Q6">
         <v>0.03</v>
       </c>
-      <c r="R5">
+      <c r="R6">
         <f t="shared" si="1"/>
         <v>0.34309999999999996</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>19</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B8" t="s">
         <v>27</v>
       </c>
-      <c r="C6">
+      <c r="C8">
         <v>6</v>
       </c>
-      <c r="D6">
+      <c r="D8">
         <v>0.43</v>
       </c>
-      <c r="E6">
+      <c r="E8">
         <v>-15</v>
       </c>
-      <c r="F6">
+      <c r="F8">
         <v>-15</v>
       </c>
-      <c r="M6">
+      <c r="H8">
+        <v>-0.05</v>
+      </c>
+      <c r="M8">
         <v>1000</v>
       </c>
-      <c r="N6">
+      <c r="N8">
         <f t="shared" si="0"/>
-        <v>18.399999999999999</v>
-      </c>
-      <c r="P6">
+        <v>18.649999999999999</v>
+      </c>
+      <c r="P8">
         <v>255</v>
       </c>
-      <c r="Q6">
+      <c r="Q8">
         <v>0.03</v>
       </c>
-      <c r="R6">
+      <c r="R8">
         <f t="shared" si="1"/>
         <v>0.43149999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>15</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B10" t="s">
         <v>28</v>
       </c>
-      <c r="C7">
+      <c r="C10">
         <v>8</v>
       </c>
-      <c r="D7">
+      <c r="D10">
         <v>0.32</v>
       </c>
-      <c r="E7">
+      <c r="E10">
         <v>-12</v>
       </c>
-      <c r="F7">
+      <c r="F10">
         <v>-14</v>
       </c>
-      <c r="M7">
+      <c r="M10">
         <v>500</v>
       </c>
-      <c r="N7">
+      <c r="N10">
         <f t="shared" si="0"/>
         <v>19.600000000000001</v>
       </c>
-      <c r="P7">
+      <c r="P10">
         <v>170</v>
       </c>
-      <c r="Q7">
+      <c r="Q10">
         <v>0.03</v>
       </c>
-      <c r="R7">
+      <c r="R10">
         <f t="shared" si="1"/>
         <v>0.32100000000000006</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>16</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B11" t="s">
         <v>29</v>
       </c>
-      <c r="C8">
+      <c r="C11">
         <v>8</v>
       </c>
-      <c r="D8">
+      <c r="D11">
         <v>0.33</v>
       </c>
-      <c r="E8">
+      <c r="E11">
         <v>-12</v>
       </c>
-      <c r="F8">
+      <c r="F11">
         <v>-14</v>
       </c>
-      <c r="M8">
+      <c r="M11">
         <v>750</v>
       </c>
-      <c r="N8">
+      <c r="N11">
         <f t="shared" si="0"/>
         <v>19.399999999999999</v>
       </c>
-      <c r="P8">
+      <c r="P11">
         <v>170</v>
       </c>
-      <c r="Q8">
+      <c r="Q11">
         <v>0.04</v>
       </c>
-      <c r="R8">
+      <c r="R11">
         <f t="shared" si="1"/>
         <v>0.33100000000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>21</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B13" t="s">
         <v>31</v>
       </c>
-      <c r="C9">
+      <c r="C13">
         <v>9</v>
       </c>
-      <c r="D9">
+      <c r="D13">
         <v>0.3</v>
       </c>
-      <c r="E9">
+      <c r="E13">
         <v>-9</v>
       </c>
-      <c r="F9">
+      <c r="F13">
         <v>-16</v>
       </c>
-      <c r="M9">
+      <c r="M13">
         <v>1000</v>
       </c>
-      <c r="N9">
+      <c r="N13">
         <f t="shared" si="0"/>
         <v>19.799999999999997</v>
       </c>
-      <c r="P9">
+      <c r="P13">
         <v>166</v>
       </c>
-      <c r="Q9">
+      <c r="Q13">
         <v>0.01</v>
       </c>
-      <c r="R9">
+      <c r="R13">
         <f t="shared" si="1"/>
         <v>0.29580000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>36</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B14" t="s">
         <v>32</v>
       </c>
-      <c r="C10">
+      <c r="C14">
         <v>6</v>
       </c>
-      <c r="D10">
+      <c r="D14">
         <v>0.38</v>
       </c>
-      <c r="E10">
+      <c r="E14">
         <v>-12</v>
       </c>
-      <c r="F10">
+      <c r="F14">
         <v>-19</v>
       </c>
-      <c r="M10">
+      <c r="M14">
         <v>1500</v>
       </c>
-      <c r="N10">
+      <c r="N14">
         <f t="shared" si="0"/>
         <v>19.400000000000002</v>
       </c>
-      <c r="P10">
+      <c r="P14">
         <v>234</v>
       </c>
-      <c r="Q10">
+      <c r="Q14">
         <v>0.01</v>
       </c>
-      <c r="R10">
+      <c r="R14">
         <f t="shared" si="1"/>
         <v>0.38419999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>24</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B16" t="s">
         <v>33</v>
       </c>
-      <c r="C11">
+      <c r="C16">
         <v>10</v>
       </c>
-      <c r="D11">
+      <c r="D16">
         <v>0.3</v>
       </c>
-      <c r="E11">
+      <c r="E16">
         <v>-13</v>
       </c>
-      <c r="F11">
+      <c r="F16">
         <v>-9</v>
       </c>
-      <c r="M11">
+      <c r="M16">
         <v>1000</v>
       </c>
-      <c r="N11">
+      <c r="N16">
         <f t="shared" si="0"/>
         <v>19.8</v>
       </c>
-      <c r="P11">
+      <c r="P16">
         <v>176</v>
       </c>
-      <c r="R11">
+      <c r="R16">
         <f t="shared" si="1"/>
         <v>0.29880000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>23</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B17" t="s">
         <v>34</v>
       </c>
-      <c r="C12">
+      <c r="C17">
         <v>9</v>
       </c>
-      <c r="D12">
+      <c r="D17">
         <v>0.32</v>
       </c>
-      <c r="E12">
+      <c r="E17">
         <v>-14</v>
       </c>
-      <c r="F12">
+      <c r="F17">
         <v>-10</v>
       </c>
-      <c r="M12">
+      <c r="M17">
         <v>1250</v>
       </c>
-      <c r="N12">
+      <c r="N17">
         <f t="shared" si="0"/>
         <v>19.8</v>
       </c>
-      <c r="P12">
+      <c r="P17">
         <f>195</f>
         <v>195</v>
       </c>
-      <c r="R12">
+      <c r="R17">
         <f t="shared" si="1"/>
         <v>0.32350000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>22</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B18" t="s">
         <v>35</v>
       </c>
-      <c r="C13">
+      <c r="C18">
         <v>7</v>
       </c>
-      <c r="D13">
+      <c r="D18">
         <v>0.37</v>
       </c>
-      <c r="E13">
+      <c r="E18">
         <v>-16</v>
       </c>
-      <c r="F13">
+      <c r="F18">
         <v>-12</v>
       </c>
-      <c r="M13">
+      <c r="M18">
         <v>1500</v>
       </c>
-      <c r="N13">
+      <c r="N18">
         <f t="shared" si="0"/>
         <v>19.600000000000001</v>
       </c>
-      <c r="P13">
+      <c r="P18">
         <v>233</v>
       </c>
-      <c r="R13">
+      <c r="R18">
         <f t="shared" si="1"/>
         <v>0.37290000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20">
+        <v>10</v>
+      </c>
+      <c r="D20">
+        <v>0.24</v>
+      </c>
+      <c r="E20">
+        <v>-10</v>
+      </c>
+      <c r="F20">
+        <v>-11</v>
+      </c>
+      <c r="M20">
+        <v>1250</v>
+      </c>
+      <c r="N20">
+        <f t="shared" si="0"/>
+        <v>19.799999999999997</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21">
+        <v>7</v>
+      </c>
+      <c r="D21">
+        <v>0.34</v>
+      </c>
+      <c r="E21">
+        <v>-12</v>
+      </c>
+      <c r="F21">
+        <v>-16</v>
+      </c>
+      <c r="M21">
+        <v>1750</v>
+      </c>
+      <c r="N21">
+        <f t="shared" si="0"/>
+        <v>19.399999999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23">
+        <v>6</v>
+      </c>
+      <c r="D23">
+        <v>0.31</v>
+      </c>
+      <c r="E23">
+        <v>-17</v>
+      </c>
+      <c r="F23">
+        <v>-10</v>
+      </c>
+      <c r="M23">
+        <v>1500</v>
+      </c>
+      <c r="N23">
+        <f t="shared" si="0"/>
+        <v>19.400000000000002</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24">
+        <v>5</v>
+      </c>
+      <c r="D24">
+        <v>0.39</v>
+      </c>
+      <c r="E24">
+        <v>-18</v>
+      </c>
+      <c r="F24">
+        <v>-13</v>
+      </c>
+      <c r="M24">
+        <v>2000</v>
+      </c>
+      <c r="N24">
+        <f t="shared" si="0"/>
+        <v>19.399999999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" t="s">
+        <v>50</v>
+      </c>
+      <c r="D25">
+        <v>0.03</v>
+      </c>
+      <c r="M25">
+        <v>100</v>
+      </c>
+      <c r="N25">
+        <f t="shared" si="0"/>
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" t="s">
+        <v>50</v>
+      </c>
+      <c r="D26">
+        <v>0.03</v>
+      </c>
+      <c r="M26">
+        <v>100</v>
+      </c>
+      <c r="N26">
+        <f t="shared" si="0"/>
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" t="s">
+        <v>51</v>
+      </c>
+      <c r="D27">
+        <v>0.05</v>
+      </c>
+      <c r="M27">
+        <v>150</v>
+      </c>
+      <c r="N27">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" t="s">
+        <v>51</v>
+      </c>
+      <c r="D28">
+        <v>0.05</v>
+      </c>
+      <c r="M28">
+        <v>150</v>
+      </c>
+      <c r="N28">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29">
+        <v>5</v>
+      </c>
+      <c r="D29">
+        <v>0.02</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>-2</v>
+      </c>
+      <c r="M29">
+        <v>250</v>
+      </c>
+      <c r="N29">
+        <f t="shared" si="0"/>
+        <v>5.8</v>
       </c>
     </row>
   </sheetData>

--- a/changes/hk416-handguards.xlsx
+++ b/changes/hk416-handguards.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WhyTh\Documents\GitHub\deadline-balancing\changes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46E07321-263F-4215-89EE-52103C2A38CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA6954C5-EC2A-47DF-8261-616ACE91DDE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <f t="shared" ref="N5:N30" si="0">C5-D5*20-E5*0.8-F5*0.6-H5*5+I5*10+J5/300</f>
+        <f t="shared" ref="N5:N29" si="0">C5-D5*20-E5*0.8-F5*0.6-H5*5+I5*10+J5/300</f>
         <v>19.200000000000003</v>
       </c>
       <c r="P5">
@@ -1552,7 +1552,7 @@
         <v>43</v>
       </c>
       <c r="C23">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D23">
         <v>0.31</v>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="N23">
         <f t="shared" si="0"/>
-        <v>19.400000000000002</v>
+        <v>17.400000000000002</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
@@ -1579,7 +1579,7 @@
         <v>44</v>
       </c>
       <c r="C24">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D24">
         <v>0.39</v>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="N24">
         <f t="shared" si="0"/>
-        <v>19.399999999999999</v>
+        <v>16.399999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
